--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/UTAH_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/UTAH_2013.xlsx
@@ -1489,7 +1489,7 @@
         <v>98</v>
       </c>
       <c r="D63">
-        <v>0.009510869565217</v>
+        <v>0.009510869565217002</v>
       </c>
     </row>
     <row r="64">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C99">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C244">
@@ -5395,7 +5395,7 @@
         <v>96</v>
       </c>
       <c r="D280">
-        <v>0.009316770186335</v>
+        <v>0.009316770186335002</v>
       </c>
     </row>
     <row r="281">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C638">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C708">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C996">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1098">
